--- a/test/owner500.xlsx
+++ b/test/owner500.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E7CF48-B0C5-42E7-92DF-903D56E839D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689FBA7E-C331-4D06-A1A6-07C9F43E0E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16785" yWindow="0" windowWidth="10920" windowHeight="15150" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="owner500" sheetId="1" r:id="rId1"/>
@@ -10729,7 +10729,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -10767,7 +10767,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
@@ -10805,7 +10805,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
@@ -10843,7 +10843,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
         <v>35</v>
@@ -10881,7 +10881,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
@@ -10919,7 +10919,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
@@ -10957,7 +10957,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
         <v>56</v>
@@ -10995,7 +10995,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
         <v>63</v>
@@ -11033,7 +11033,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
@@ -11071,7 +11071,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
         <v>77</v>
@@ -11109,7 +11109,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
         <v>84</v>
@@ -11147,7 +11147,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
         <v>91</v>
@@ -11185,7 +11185,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
@@ -11223,7 +11223,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>105</v>
@@ -11261,7 +11261,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
         <v>112</v>
@@ -11299,7 +11299,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
         <v>119</v>
@@ -11337,7 +11337,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
         <v>126</v>
@@ -11375,7 +11375,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
         <v>133</v>
@@ -11413,7 +11413,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
         <v>140</v>
@@ -11451,7 +11451,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
         <v>147</v>
@@ -11489,7 +11489,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
         <v>154</v>
@@ -11527,7 +11527,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
         <v>161</v>
@@ -11565,7 +11565,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
         <v>168</v>
@@ -11603,7 +11603,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
         <v>175</v>
@@ -11641,7 +11641,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
         <v>182</v>
@@ -11679,7 +11679,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
         <v>189</v>
@@ -11717,7 +11717,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
         <v>196</v>
@@ -11755,7 +11755,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
         <v>203</v>
@@ -11793,7 +11793,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
         <v>210</v>
@@ -11831,7 +11831,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
         <v>217</v>
@@ -11869,7 +11869,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
         <v>224</v>
@@ -11907,7 +11907,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
         <v>231</v>
@@ -11945,7 +11945,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
         <v>238</v>
@@ -11983,7 +11983,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
         <v>245</v>
@@ -12021,7 +12021,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
         <v>252</v>
@@ -12059,7 +12059,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
         <v>259</v>
@@ -12097,7 +12097,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B38" t="s">
         <v>266</v>
@@ -12135,7 +12135,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
         <v>273</v>
@@ -12173,7 +12173,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
         <v>280</v>
@@ -12211,7 +12211,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
         <v>287</v>
@@ -12249,7 +12249,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B42" t="s">
         <v>294</v>
@@ -12287,7 +12287,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
         <v>301</v>
@@ -12325,7 +12325,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B44" t="s">
         <v>308</v>
@@ -12363,7 +12363,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B45" t="s">
         <v>315</v>
@@ -12401,7 +12401,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
         <v>322</v>
@@ -12439,7 +12439,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
         <v>329</v>
@@ -12477,7 +12477,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
         <v>336</v>
@@ -12515,7 +12515,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B49" t="s">
         <v>343</v>
@@ -12553,7 +12553,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B50" t="s">
         <v>350</v>
@@ -12591,7 +12591,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B51" t="s">
         <v>357</v>
@@ -12629,7 +12629,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B52" t="s">
         <v>364</v>
@@ -12667,7 +12667,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B53" t="s">
         <v>371</v>
@@ -12705,7 +12705,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B54" t="s">
         <v>378</v>
@@ -12743,7 +12743,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
         <v>385</v>
@@ -12781,7 +12781,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
         <v>392</v>
@@ -12819,7 +12819,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B57" t="s">
         <v>399</v>
@@ -12857,7 +12857,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
         <v>406</v>
@@ -12895,7 +12895,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
         <v>413</v>
@@ -12933,7 +12933,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
         <v>420</v>
@@ -12971,7 +12971,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B61" t="s">
         <v>427</v>
@@ -13009,7 +13009,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B62" t="s">
         <v>434</v>
@@ -13047,7 +13047,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B63" t="s">
         <v>441</v>
@@ -13085,7 +13085,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
         <v>448</v>
@@ -13123,7 +13123,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
         <v>455</v>
@@ -13161,7 +13161,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
         <v>462</v>
@@ -13199,7 +13199,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
         <v>469</v>
@@ -13237,7 +13237,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B68" t="s">
         <v>476</v>
@@ -13275,7 +13275,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B69" t="s">
         <v>483</v>
@@ -13313,7 +13313,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B70" t="s">
         <v>490</v>
@@ -13351,7 +13351,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
         <v>497</v>
@@ -13389,7 +13389,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B72" t="s">
         <v>504</v>
@@ -13427,7 +13427,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
         <v>511</v>
@@ -13464,6 +13464,9 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>65</v>
+      </c>
       <c r="B74" t="s">
         <v>518</v>
       </c>
@@ -13499,6 +13502,9 @@
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>65</v>
+      </c>
       <c r="B75" t="s">
         <v>525</v>
       </c>
@@ -13534,6 +13540,9 @@
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>65</v>
+      </c>
       <c r="B76" t="s">
         <v>532</v>
       </c>
@@ -13569,6 +13578,9 @@
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>65</v>
+      </c>
       <c r="B77" t="s">
         <v>539</v>
       </c>
@@ -13604,6 +13616,9 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>65</v>
+      </c>
       <c r="B78" t="s">
         <v>546</v>
       </c>
@@ -13639,6 +13654,9 @@
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>65</v>
+      </c>
       <c r="B79" t="s">
         <v>553</v>
       </c>
@@ -13674,6 +13692,9 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>65</v>
+      </c>
       <c r="B80" t="s">
         <v>560</v>
       </c>
@@ -13708,7 +13729,10 @@
         <v>566</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>65</v>
+      </c>
       <c r="B81" t="s">
         <v>567</v>
       </c>
@@ -13743,7 +13767,10 @@
         <v>573</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>65</v>
+      </c>
       <c r="B82" t="s">
         <v>574</v>
       </c>
@@ -13778,7 +13805,10 @@
         <v>580</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>65</v>
+      </c>
       <c r="B83" t="s">
         <v>581</v>
       </c>
@@ -13813,7 +13843,10 @@
         <v>587</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>65</v>
+      </c>
       <c r="B84" t="s">
         <v>588</v>
       </c>
@@ -13848,7 +13881,10 @@
         <v>594</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>65</v>
+      </c>
       <c r="B85" t="s">
         <v>595</v>
       </c>
@@ -13883,7 +13919,10 @@
         <v>600</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>65</v>
+      </c>
       <c r="B86" t="s">
         <v>601</v>
       </c>
@@ -13918,7 +13957,10 @@
         <v>607</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>65</v>
+      </c>
       <c r="B87" t="s">
         <v>608</v>
       </c>
@@ -13953,7 +13995,10 @@
         <v>614</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>65</v>
+      </c>
       <c r="B88" t="s">
         <v>615</v>
       </c>
@@ -13988,7 +14033,10 @@
         <v>621</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>65</v>
+      </c>
       <c r="B89" t="s">
         <v>622</v>
       </c>
@@ -14023,7 +14071,10 @@
         <v>628</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>65</v>
+      </c>
       <c r="B90" t="s">
         <v>629</v>
       </c>
@@ -14058,7 +14109,10 @@
         <v>635</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>65</v>
+      </c>
       <c r="B91" t="s">
         <v>636</v>
       </c>
@@ -14093,7 +14147,10 @@
         <v>642</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>65</v>
+      </c>
       <c r="B92" t="s">
         <v>643</v>
       </c>
@@ -14128,7 +14185,10 @@
         <v>649</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>65</v>
+      </c>
       <c r="B93" t="s">
         <v>650</v>
       </c>
@@ -14163,7 +14223,10 @@
         <v>656</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>65</v>
+      </c>
       <c r="B94" t="s">
         <v>657</v>
       </c>
@@ -14198,7 +14261,10 @@
         <v>663</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>65</v>
+      </c>
       <c r="B95" t="s">
         <v>664</v>
       </c>
@@ -14233,7 +14299,10 @@
         <v>670</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>65</v>
+      </c>
       <c r="B96" t="s">
         <v>671</v>
       </c>
@@ -14268,7 +14337,10 @@
         <v>677</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>65</v>
+      </c>
       <c r="B97" t="s">
         <v>678</v>
       </c>
@@ -14303,7 +14375,10 @@
         <v>684</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>65</v>
+      </c>
       <c r="B98" t="s">
         <v>685</v>
       </c>
@@ -14338,7 +14413,10 @@
         <v>691</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>65</v>
+      </c>
       <c r="B99" t="s">
         <v>692</v>
       </c>
@@ -14373,7 +14451,10 @@
         <v>698</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>65</v>
+      </c>
       <c r="B100" t="s">
         <v>699</v>
       </c>
@@ -14408,7 +14489,10 @@
         <v>705</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>65</v>
+      </c>
       <c r="B101" t="s">
         <v>706</v>
       </c>
@@ -14443,7 +14527,10 @@
         <v>712</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>65</v>
+      </c>
       <c r="B102" t="s">
         <v>713</v>
       </c>
@@ -14478,7 +14565,10 @@
         <v>719</v>
       </c>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>65</v>
+      </c>
       <c r="B103" t="s">
         <v>720</v>
       </c>
@@ -14513,7 +14603,10 @@
         <v>726</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>65</v>
+      </c>
       <c r="B104" t="s">
         <v>727</v>
       </c>
@@ -14548,7 +14641,10 @@
         <v>733</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>65</v>
+      </c>
       <c r="B105" t="s">
         <v>734</v>
       </c>
@@ -14583,7 +14679,10 @@
         <v>740</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>65</v>
+      </c>
       <c r="B106" t="s">
         <v>741</v>
       </c>
@@ -14618,7 +14717,10 @@
         <v>747</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>65</v>
+      </c>
       <c r="B107" t="s">
         <v>748</v>
       </c>
@@ -14653,7 +14755,10 @@
         <v>754</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>65</v>
+      </c>
       <c r="B108" t="s">
         <v>755</v>
       </c>
@@ -14688,7 +14793,10 @@
         <v>761</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>65</v>
+      </c>
       <c r="B109" t="s">
         <v>762</v>
       </c>
@@ -14723,7 +14831,10 @@
         <v>768</v>
       </c>
     </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>65</v>
+      </c>
       <c r="B110" t="s">
         <v>769</v>
       </c>
@@ -14758,7 +14869,10 @@
         <v>775</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>65</v>
+      </c>
       <c r="B111" t="s">
         <v>776</v>
       </c>
@@ -14793,7 +14907,10 @@
         <v>782</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>65</v>
+      </c>
       <c r="B112" t="s">
         <v>783</v>
       </c>
@@ -14828,7 +14945,10 @@
         <v>789</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>65</v>
+      </c>
       <c r="B113" t="s">
         <v>790</v>
       </c>
@@ -14863,7 +14983,10 @@
         <v>796</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>65</v>
+      </c>
       <c r="B114" t="s">
         <v>797</v>
       </c>
@@ -14898,7 +15021,10 @@
         <v>803</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>65</v>
+      </c>
       <c r="B115" t="s">
         <v>804</v>
       </c>
@@ -14933,7 +15059,10 @@
         <v>810</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>65</v>
+      </c>
       <c r="B116" t="s">
         <v>811</v>
       </c>
@@ -14968,7 +15097,10 @@
         <v>817</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>65</v>
+      </c>
       <c r="B117" t="s">
         <v>818</v>
       </c>
@@ -15003,7 +15135,10 @@
         <v>824</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>65</v>
+      </c>
       <c r="B118" t="s">
         <v>825</v>
       </c>
@@ -15038,7 +15173,10 @@
         <v>831</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>65</v>
+      </c>
       <c r="B119" t="s">
         <v>832</v>
       </c>
@@ -15073,7 +15211,10 @@
         <v>838</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>65</v>
+      </c>
       <c r="B120" t="s">
         <v>797</v>
       </c>
@@ -15108,7 +15249,10 @@
         <v>844</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>65</v>
+      </c>
       <c r="B121" t="s">
         <v>845</v>
       </c>
@@ -15143,7 +15287,10 @@
         <v>851</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>65</v>
+      </c>
       <c r="B122" t="s">
         <v>852</v>
       </c>
@@ -15178,7 +15325,10 @@
         <v>858</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>65</v>
+      </c>
       <c r="B123" t="s">
         <v>859</v>
       </c>
@@ -15213,7 +15363,10 @@
         <v>865</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>65</v>
+      </c>
       <c r="B124" t="s">
         <v>866</v>
       </c>
@@ -15248,7 +15401,10 @@
         <v>872</v>
       </c>
     </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>65</v>
+      </c>
       <c r="B125" t="s">
         <v>873</v>
       </c>
@@ -15283,7 +15439,10 @@
         <v>879</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>65</v>
+      </c>
       <c r="B126" t="s">
         <v>880</v>
       </c>
@@ -15318,7 +15477,10 @@
         <v>886</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>65</v>
+      </c>
       <c r="B127" t="s">
         <v>887</v>
       </c>
@@ -15353,7 +15515,10 @@
         <v>893</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>65</v>
+      </c>
       <c r="B128" t="s">
         <v>894</v>
       </c>
@@ -15388,7 +15553,10 @@
         <v>900</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>65</v>
+      </c>
       <c r="B129" t="s">
         <v>901</v>
       </c>
@@ -15423,7 +15591,10 @@
         <v>907</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>65</v>
+      </c>
       <c r="B130" t="s">
         <v>908</v>
       </c>
@@ -15458,7 +15629,10 @@
         <v>914</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>65</v>
+      </c>
       <c r="B131" t="s">
         <v>915</v>
       </c>
@@ -15493,7 +15667,10 @@
         <v>921</v>
       </c>
     </row>
-    <row r="132" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>65</v>
+      </c>
       <c r="B132" t="s">
         <v>922</v>
       </c>
@@ -15528,7 +15705,10 @@
         <v>928</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>65</v>
+      </c>
       <c r="B133" t="s">
         <v>929</v>
       </c>
@@ -15563,7 +15743,10 @@
         <v>935</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>65</v>
+      </c>
       <c r="B134" t="s">
         <v>936</v>
       </c>
@@ -15598,7 +15781,10 @@
         <v>942</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>65</v>
+      </c>
       <c r="B135" t="s">
         <v>943</v>
       </c>
@@ -15633,7 +15819,10 @@
         <v>949</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>65</v>
+      </c>
       <c r="B136" t="s">
         <v>950</v>
       </c>
@@ -15668,7 +15857,10 @@
         <v>956</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>65</v>
+      </c>
       <c r="B137" t="s">
         <v>957</v>
       </c>
@@ -15703,7 +15895,10 @@
         <v>963</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>65</v>
+      </c>
       <c r="B138" t="s">
         <v>964</v>
       </c>
@@ -15738,7 +15933,10 @@
         <v>970</v>
       </c>
     </row>
-    <row r="139" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>65</v>
+      </c>
       <c r="B139" t="s">
         <v>971</v>
       </c>
@@ -15773,7 +15971,10 @@
         <v>977</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>65</v>
+      </c>
       <c r="B140" t="s">
         <v>978</v>
       </c>
@@ -15808,7 +16009,10 @@
         <v>984</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>65</v>
+      </c>
       <c r="B141" t="s">
         <v>985</v>
       </c>
@@ -15843,7 +16047,10 @@
         <v>991</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>65</v>
+      </c>
       <c r="B142" t="s">
         <v>992</v>
       </c>
@@ -15878,7 +16085,10 @@
         <v>998</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>65</v>
+      </c>
       <c r="B143" t="s">
         <v>999</v>
       </c>
@@ -15913,7 +16123,10 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>65</v>
+      </c>
       <c r="B144" t="s">
         <v>1006</v>
       </c>
@@ -15948,7 +16161,10 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>65</v>
+      </c>
       <c r="B145" t="s">
         <v>1013</v>
       </c>
@@ -15983,7 +16199,10 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>65</v>
+      </c>
       <c r="B146" t="s">
         <v>1020</v>
       </c>
@@ -16018,7 +16237,10 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>65</v>
+      </c>
       <c r="B147" t="s">
         <v>1027</v>
       </c>
@@ -16053,7 +16275,10 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="148" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>65</v>
+      </c>
       <c r="B148" t="s">
         <v>1034</v>
       </c>
@@ -16088,7 +16313,10 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="149" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>65</v>
+      </c>
       <c r="B149" t="s">
         <v>1041</v>
       </c>
@@ -16123,7 +16351,10 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="150" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>65</v>
+      </c>
       <c r="B150" t="s">
         <v>1048</v>
       </c>
@@ -16158,7 +16389,10 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="151" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>65</v>
+      </c>
       <c r="B151" t="s">
         <v>1055</v>
       </c>
@@ -16193,7 +16427,10 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="152" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>65</v>
+      </c>
       <c r="B152" t="s">
         <v>1062</v>
       </c>
@@ -16228,7 +16465,10 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="153" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>65</v>
+      </c>
       <c r="B153" t="s">
         <v>1069</v>
       </c>
@@ -16263,7 +16503,10 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="154" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>65</v>
+      </c>
       <c r="B154" t="s">
         <v>1076</v>
       </c>
@@ -16298,7 +16541,10 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="155" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>65</v>
+      </c>
       <c r="B155" t="s">
         <v>1083</v>
       </c>
@@ -16333,7 +16579,10 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="156" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>65</v>
+      </c>
       <c r="B156" t="s">
         <v>1090</v>
       </c>
@@ -16368,7 +16617,10 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="157" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>65</v>
+      </c>
       <c r="B157" t="s">
         <v>1097</v>
       </c>
@@ -16403,7 +16655,10 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="158" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>65</v>
+      </c>
       <c r="B158" t="s">
         <v>1104</v>
       </c>
@@ -16438,7 +16693,10 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="159" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>65</v>
+      </c>
       <c r="B159" t="s">
         <v>1111</v>
       </c>
@@ -16473,7 +16731,10 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="160" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>65</v>
+      </c>
       <c r="B160" t="s">
         <v>1118</v>
       </c>
@@ -16508,7 +16769,10 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="161" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>65</v>
+      </c>
       <c r="B161" t="s">
         <v>1125</v>
       </c>
@@ -16543,7 +16807,10 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="162" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>65</v>
+      </c>
       <c r="B162" t="s">
         <v>1132</v>
       </c>
@@ -16578,7 +16845,10 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>65</v>
+      </c>
       <c r="B163" t="s">
         <v>1139</v>
       </c>
@@ -16613,7 +16883,10 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="164" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>65</v>
+      </c>
       <c r="B164" t="s">
         <v>1146</v>
       </c>
@@ -16648,7 +16921,10 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="165" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>65</v>
+      </c>
       <c r="B165" t="s">
         <v>1153</v>
       </c>
@@ -16683,7 +16959,10 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="166" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>65</v>
+      </c>
       <c r="B166" t="s">
         <v>1160</v>
       </c>
@@ -16718,7 +16997,10 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="167" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>65</v>
+      </c>
       <c r="B167" t="s">
         <v>1167</v>
       </c>
@@ -16753,7 +17035,10 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>65</v>
+      </c>
       <c r="B168" t="s">
         <v>1174</v>
       </c>
@@ -16788,7 +17073,10 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="169" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>65</v>
+      </c>
       <c r="B169" t="s">
         <v>1181</v>
       </c>
@@ -16823,7 +17111,10 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="170" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>65</v>
+      </c>
       <c r="B170" t="s">
         <v>1188</v>
       </c>
@@ -16858,7 +17149,10 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="171" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>65</v>
+      </c>
       <c r="B171" t="s">
         <v>1195</v>
       </c>
@@ -16893,7 +17187,10 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>65</v>
+      </c>
       <c r="B172" t="s">
         <v>1202</v>
       </c>
@@ -16928,7 +17225,10 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>65</v>
+      </c>
       <c r="B173" t="s">
         <v>1209</v>
       </c>
@@ -16963,7 +17263,10 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="174" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>65</v>
+      </c>
       <c r="B174" t="s">
         <v>1216</v>
       </c>
@@ -16998,7 +17301,10 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="175" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>65</v>
+      </c>
       <c r="B175" t="s">
         <v>1223</v>
       </c>
@@ -17033,7 +17339,10 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="176" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>65</v>
+      </c>
       <c r="B176" t="s">
         <v>1230</v>
       </c>
@@ -17068,7 +17377,10 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="177" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>65</v>
+      </c>
       <c r="B177" t="s">
         <v>1237</v>
       </c>
@@ -17103,7 +17415,10 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="178" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>65</v>
+      </c>
       <c r="B178" t="s">
         <v>1244</v>
       </c>
@@ -17138,7 +17453,10 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="179" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>65</v>
+      </c>
       <c r="B179" t="s">
         <v>1251</v>
       </c>
@@ -17173,7 +17491,10 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="180" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>65</v>
+      </c>
       <c r="B180" t="s">
         <v>1258</v>
       </c>
@@ -17208,7 +17529,10 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="181" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>65</v>
+      </c>
       <c r="B181" t="s">
         <v>1265</v>
       </c>
@@ -17243,7 +17567,10 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="182" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>65</v>
+      </c>
       <c r="B182" t="s">
         <v>1272</v>
       </c>
@@ -17278,7 +17605,10 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="183" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>65</v>
+      </c>
       <c r="B183" t="s">
         <v>1279</v>
       </c>
@@ -17313,7 +17643,10 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="184" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>65</v>
+      </c>
       <c r="B184" t="s">
         <v>1286</v>
       </c>
@@ -17348,7 +17681,10 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="185" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>65</v>
+      </c>
       <c r="B185" t="s">
         <v>1293</v>
       </c>
@@ -17383,7 +17719,10 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="186" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>65</v>
+      </c>
       <c r="B186" t="s">
         <v>1300</v>
       </c>
@@ -17418,7 +17757,10 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="187" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>65</v>
+      </c>
       <c r="B187" t="s">
         <v>1307</v>
       </c>
@@ -17453,7 +17795,10 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="188" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>65</v>
+      </c>
       <c r="B188" t="s">
         <v>1314</v>
       </c>
@@ -17488,7 +17833,10 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="189" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>65</v>
+      </c>
       <c r="B189" t="s">
         <v>1321</v>
       </c>
@@ -17523,7 +17871,10 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="190" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>65</v>
+      </c>
       <c r="B190" t="s">
         <v>1328</v>
       </c>
@@ -17558,7 +17909,10 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="191" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>65</v>
+      </c>
       <c r="B191" t="s">
         <v>1335</v>
       </c>
@@ -17593,7 +17947,10 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="192" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>65</v>
+      </c>
       <c r="B192" t="s">
         <v>1342</v>
       </c>
@@ -17628,7 +17985,10 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="193" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>65</v>
+      </c>
       <c r="B193" t="s">
         <v>1349</v>
       </c>
@@ -17663,7 +18023,10 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="194" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>65</v>
+      </c>
       <c r="B194" t="s">
         <v>1356</v>
       </c>
@@ -17698,7 +18061,10 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="195" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>65</v>
+      </c>
       <c r="B195" t="s">
         <v>1363</v>
       </c>
@@ -17733,7 +18099,10 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="196" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>65</v>
+      </c>
       <c r="B196" t="s">
         <v>1370</v>
       </c>
@@ -17768,7 +18137,10 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="197" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>65</v>
+      </c>
       <c r="B197" t="s">
         <v>1377</v>
       </c>
@@ -17803,7 +18175,10 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="198" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>65</v>
+      </c>
       <c r="B198" t="s">
         <v>1384</v>
       </c>
@@ -17838,7 +18213,10 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="199" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>65</v>
+      </c>
       <c r="B199" t="s">
         <v>1391</v>
       </c>
@@ -17873,7 +18251,10 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="200" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>65</v>
+      </c>
       <c r="B200" t="s">
         <v>1398</v>
       </c>
@@ -17908,7 +18289,10 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="201" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>65</v>
+      </c>
       <c r="B201" t="s">
         <v>1405</v>
       </c>
@@ -17943,7 +18327,10 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="202" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>65</v>
+      </c>
       <c r="B202" t="s">
         <v>1412</v>
       </c>
@@ -17978,7 +18365,10 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="203" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>65</v>
+      </c>
       <c r="B203" t="s">
         <v>1419</v>
       </c>
@@ -18013,7 +18403,10 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="204" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>65</v>
+      </c>
       <c r="B204" t="s">
         <v>1426</v>
       </c>
@@ -18048,7 +18441,10 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="205" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>65</v>
+      </c>
       <c r="B205" t="s">
         <v>1433</v>
       </c>
@@ -18083,7 +18479,10 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="206" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>65</v>
+      </c>
       <c r="B206" t="s">
         <v>1440</v>
       </c>
@@ -18118,7 +18517,10 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="207" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>65</v>
+      </c>
       <c r="B207" t="s">
         <v>1447</v>
       </c>
@@ -18153,7 +18555,10 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="208" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>65</v>
+      </c>
       <c r="B208" t="s">
         <v>1454</v>
       </c>
@@ -18188,7 +18593,10 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="209" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>65</v>
+      </c>
       <c r="B209" t="s">
         <v>1461</v>
       </c>
@@ -18223,7 +18631,10 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="210" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>65</v>
+      </c>
       <c r="B210" t="s">
         <v>1468</v>
       </c>
@@ -18258,7 +18669,10 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="211" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>65</v>
+      </c>
       <c r="B211" t="s">
         <v>1475</v>
       </c>
@@ -18293,7 +18707,10 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="212" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A212">
+        <v>65</v>
+      </c>
       <c r="B212" t="s">
         <v>1482</v>
       </c>
@@ -18328,7 +18745,10 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="213" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A213">
+        <v>65</v>
+      </c>
       <c r="B213" t="s">
         <v>1489</v>
       </c>
@@ -18363,7 +18783,10 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="214" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A214">
+        <v>65</v>
+      </c>
       <c r="B214" t="s">
         <v>1496</v>
       </c>
@@ -18398,7 +18821,10 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="215" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A215">
+        <v>65</v>
+      </c>
       <c r="B215" t="s">
         <v>1503</v>
       </c>
@@ -18433,7 +18859,10 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="216" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>65</v>
+      </c>
       <c r="B216" t="s">
         <v>1510</v>
       </c>
@@ -18468,7 +18897,10 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="217" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>65</v>
+      </c>
       <c r="B217" t="s">
         <v>1517</v>
       </c>
@@ -18503,7 +18935,10 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="218" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>65</v>
+      </c>
       <c r="B218" t="s">
         <v>1524</v>
       </c>
@@ -18538,7 +18973,10 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="219" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A219">
+        <v>65</v>
+      </c>
       <c r="B219" t="s">
         <v>1531</v>
       </c>
@@ -18573,7 +19011,10 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="220" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A220">
+        <v>65</v>
+      </c>
       <c r="B220" t="s">
         <v>748</v>
       </c>
@@ -18608,7 +19049,10 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="221" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A221">
+        <v>65</v>
+      </c>
       <c r="B221" t="s">
         <v>1544</v>
       </c>
@@ -18643,7 +19087,10 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="222" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>65</v>
+      </c>
       <c r="B222" t="s">
         <v>1551</v>
       </c>
@@ -18678,7 +19125,10 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="223" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A223">
+        <v>65</v>
+      </c>
       <c r="B223" t="s">
         <v>1558</v>
       </c>
@@ -18713,7 +19163,10 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="224" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>65</v>
+      </c>
       <c r="B224" t="s">
         <v>1565</v>
       </c>
@@ -18748,7 +19201,10 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="225" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A225">
+        <v>65</v>
+      </c>
       <c r="B225" t="s">
         <v>1572</v>
       </c>
@@ -18783,7 +19239,10 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="226" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>65</v>
+      </c>
       <c r="B226" t="s">
         <v>1579</v>
       </c>
@@ -18818,7 +19277,10 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="227" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A227">
+        <v>65</v>
+      </c>
       <c r="B227" t="s">
         <v>1586</v>
       </c>
@@ -18853,7 +19315,10 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="228" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>65</v>
+      </c>
       <c r="B228" t="s">
         <v>1593</v>
       </c>
@@ -18888,7 +19353,10 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="229" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A229">
+        <v>65</v>
+      </c>
       <c r="B229" t="s">
         <v>1600</v>
       </c>
@@ -18923,7 +19391,10 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="230" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A230">
+        <v>65</v>
+      </c>
       <c r="B230" t="s">
         <v>1607</v>
       </c>
@@ -18958,7 +19429,10 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="231" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A231">
+        <v>65</v>
+      </c>
       <c r="B231" t="s">
         <v>1614</v>
       </c>
@@ -18993,7 +19467,10 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="232" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A232">
+        <v>65</v>
+      </c>
       <c r="B232" t="s">
         <v>1621</v>
       </c>
@@ -19028,7 +19505,10 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="233" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A233">
+        <v>65</v>
+      </c>
       <c r="B233" t="s">
         <v>1628</v>
       </c>
@@ -19063,7 +19543,10 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="234" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A234">
+        <v>65</v>
+      </c>
       <c r="B234" t="s">
         <v>1635</v>
       </c>
@@ -19098,7 +19581,10 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="235" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A235">
+        <v>65</v>
+      </c>
       <c r="B235" t="s">
         <v>1642</v>
       </c>
@@ -19133,7 +19619,10 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="236" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>65</v>
+      </c>
       <c r="B236" t="s">
         <v>1649</v>
       </c>
@@ -19168,7 +19657,10 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="237" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A237">
+        <v>65</v>
+      </c>
       <c r="B237" t="s">
         <v>1656</v>
       </c>
@@ -19203,7 +19695,10 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="238" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A238">
+        <v>65</v>
+      </c>
       <c r="B238" t="s">
         <v>1663</v>
       </c>
@@ -19238,7 +19733,10 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="239" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A239">
+        <v>65</v>
+      </c>
       <c r="B239" t="s">
         <v>1670</v>
       </c>
@@ -19273,7 +19771,10 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="240" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A240">
+        <v>65</v>
+      </c>
       <c r="B240" t="s">
         <v>1677</v>
       </c>
@@ -19308,7 +19809,10 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="241" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A241">
+        <v>65</v>
+      </c>
       <c r="B241" t="s">
         <v>1684</v>
       </c>
@@ -19343,7 +19847,10 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="242" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A242">
+        <v>65</v>
+      </c>
       <c r="B242" t="s">
         <v>1691</v>
       </c>
@@ -19378,7 +19885,10 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="243" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A243">
+        <v>65</v>
+      </c>
       <c r="B243" t="s">
         <v>1698</v>
       </c>
@@ -19413,7 +19923,10 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="244" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A244">
+        <v>65</v>
+      </c>
       <c r="B244" t="s">
         <v>1705</v>
       </c>
@@ -19448,7 +19961,10 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="245" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A245">
+        <v>65</v>
+      </c>
       <c r="B245" t="s">
         <v>1712</v>
       </c>
@@ -19483,7 +19999,10 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="246" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A246">
+        <v>65</v>
+      </c>
       <c r="B246" t="s">
         <v>1719</v>
       </c>
@@ -19518,7 +20037,10 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="247" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A247">
+        <v>65</v>
+      </c>
       <c r="B247" t="s">
         <v>1726</v>
       </c>
@@ -19553,7 +20075,10 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="248" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A248">
+        <v>65</v>
+      </c>
       <c r="B248" t="s">
         <v>1733</v>
       </c>
@@ -19588,7 +20113,10 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="249" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A249">
+        <v>65</v>
+      </c>
       <c r="B249" t="s">
         <v>1740</v>
       </c>
@@ -19623,7 +20151,10 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="250" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A250">
+        <v>65</v>
+      </c>
       <c r="B250" t="s">
         <v>1747</v>
       </c>
@@ -19658,7 +20189,10 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="251" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A251">
+        <v>65</v>
+      </c>
       <c r="B251" t="s">
         <v>1754</v>
       </c>
@@ -19693,7 +20227,10 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="252" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A252">
+        <v>65</v>
+      </c>
       <c r="B252" t="s">
         <v>1761</v>
       </c>
@@ -19728,7 +20265,10 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="253" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A253">
+        <v>65</v>
+      </c>
       <c r="B253" t="s">
         <v>1768</v>
       </c>
@@ -19763,7 +20303,10 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="254" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A254">
+        <v>65</v>
+      </c>
       <c r="B254" t="s">
         <v>1775</v>
       </c>
@@ -19798,7 +20341,10 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="255" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A255">
+        <v>65</v>
+      </c>
       <c r="B255" t="s">
         <v>1782</v>
       </c>
@@ -19833,7 +20379,10 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="256" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A256">
+        <v>65</v>
+      </c>
       <c r="B256" t="s">
         <v>1789</v>
       </c>
@@ -19868,7 +20417,10 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="257" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A257">
+        <v>65</v>
+      </c>
       <c r="B257" t="s">
         <v>1796</v>
       </c>
@@ -19903,7 +20455,10 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="258" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A258">
+        <v>65</v>
+      </c>
       <c r="B258" t="s">
         <v>1803</v>
       </c>
@@ -19938,7 +20493,10 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="259" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A259">
+        <v>65</v>
+      </c>
       <c r="B259" t="s">
         <v>1810</v>
       </c>
@@ -19973,7 +20531,10 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="260" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>65</v>
+      </c>
       <c r="B260" t="s">
         <v>1817</v>
       </c>
@@ -20008,7 +20569,10 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="261" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>65</v>
+      </c>
       <c r="B261" t="s">
         <v>1824</v>
       </c>
@@ -20043,7 +20607,10 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="262" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>65</v>
+      </c>
       <c r="B262" t="s">
         <v>1831</v>
       </c>
@@ -20078,7 +20645,10 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="263" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>65</v>
+      </c>
       <c r="B263" t="s">
         <v>1838</v>
       </c>
@@ -20113,7 +20683,10 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="264" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>65</v>
+      </c>
       <c r="B264" t="s">
         <v>1586</v>
       </c>
@@ -20148,7 +20721,10 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="265" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>65</v>
+      </c>
       <c r="B265" t="s">
         <v>1851</v>
       </c>
@@ -20183,7 +20759,10 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="266" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A266">
+        <v>65</v>
+      </c>
       <c r="B266" t="s">
         <v>1858</v>
       </c>
@@ -20218,7 +20797,10 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="267" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>65</v>
+      </c>
       <c r="B267" t="s">
         <v>1865</v>
       </c>
@@ -20253,7 +20835,10 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="268" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A268">
+        <v>65</v>
+      </c>
       <c r="B268" t="s">
         <v>1872</v>
       </c>
@@ -20288,7 +20873,10 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="269" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A269">
+        <v>65</v>
+      </c>
       <c r="B269" t="s">
         <v>1879</v>
       </c>
@@ -20323,7 +20911,10 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="270" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>65</v>
+      </c>
       <c r="B270" t="s">
         <v>1886</v>
       </c>
@@ -20358,7 +20949,10 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="271" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>65</v>
+      </c>
       <c r="B271" t="s">
         <v>1893</v>
       </c>
@@ -20393,7 +20987,10 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="272" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>65</v>
+      </c>
       <c r="B272" t="s">
         <v>1900</v>
       </c>
@@ -20428,7 +21025,10 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="273" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>65</v>
+      </c>
       <c r="B273" t="s">
         <v>1907</v>
       </c>
@@ -20463,7 +21063,10 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="274" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>65</v>
+      </c>
       <c r="B274" t="s">
         <v>1914</v>
       </c>
@@ -20498,7 +21101,10 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="275" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>65</v>
+      </c>
       <c r="B275" t="s">
         <v>1921</v>
       </c>
@@ -20533,7 +21139,10 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="276" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A276">
+        <v>65</v>
+      </c>
       <c r="B276" t="s">
         <v>1139</v>
       </c>
@@ -20568,7 +21177,10 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="277" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A277">
+        <v>65</v>
+      </c>
       <c r="B277" t="s">
         <v>1934</v>
       </c>
@@ -20603,7 +21215,10 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="278" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A278">
+        <v>65</v>
+      </c>
       <c r="B278" t="s">
         <v>1941</v>
       </c>
@@ -20638,7 +21253,10 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="279" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A279">
+        <v>65</v>
+      </c>
       <c r="B279" t="s">
         <v>1948</v>
       </c>
@@ -20673,7 +21291,10 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="280" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A280">
+        <v>65</v>
+      </c>
       <c r="B280" t="s">
         <v>1139</v>
       </c>
@@ -20708,7 +21329,10 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="281" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>65</v>
+      </c>
       <c r="B281" t="s">
         <v>1961</v>
       </c>
@@ -20743,7 +21367,10 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="282" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A282">
+        <v>65</v>
+      </c>
       <c r="B282" t="s">
         <v>1968</v>
       </c>
@@ -20778,7 +21405,10 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="283" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A283">
+        <v>65</v>
+      </c>
       <c r="B283" t="s">
         <v>1975</v>
       </c>
@@ -20813,7 +21443,10 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="284" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A284">
+        <v>65</v>
+      </c>
       <c r="B284" t="s">
         <v>1982</v>
       </c>
@@ -20848,7 +21481,10 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="285" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A285">
+        <v>65</v>
+      </c>
       <c r="B285" t="s">
         <v>1989</v>
       </c>
@@ -20883,7 +21519,10 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="286" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A286">
+        <v>65</v>
+      </c>
       <c r="B286" t="s">
         <v>1996</v>
       </c>
@@ -20918,7 +21557,10 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="287" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A287">
+        <v>65</v>
+      </c>
       <c r="B287" t="s">
         <v>2003</v>
       </c>
@@ -20953,7 +21595,10 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="288" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A288">
+        <v>65</v>
+      </c>
       <c r="B288" t="s">
         <v>2010</v>
       </c>
@@ -20988,7 +21633,10 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="289" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A289">
+        <v>65</v>
+      </c>
       <c r="B289" t="s">
         <v>2017</v>
       </c>
@@ -21023,7 +21671,10 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="290" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A290">
+        <v>65</v>
+      </c>
       <c r="B290" t="s">
         <v>2024</v>
       </c>
@@ -21058,7 +21709,10 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="291" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>65</v>
+      </c>
       <c r="B291" t="s">
         <v>2031</v>
       </c>
@@ -21093,7 +21747,10 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="292" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>65</v>
+      </c>
       <c r="B292" t="s">
         <v>2038</v>
       </c>
@@ -21128,7 +21785,10 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="293" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A293">
+        <v>65</v>
+      </c>
       <c r="B293" t="s">
         <v>2045</v>
       </c>
@@ -21163,7 +21823,10 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="294" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A294">
+        <v>65</v>
+      </c>
       <c r="B294" t="s">
         <v>2052</v>
       </c>
@@ -21198,7 +21861,10 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="295" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A295">
+        <v>65</v>
+      </c>
       <c r="B295" t="s">
         <v>2059</v>
       </c>
@@ -21233,7 +21899,10 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="296" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A296">
+        <v>65</v>
+      </c>
       <c r="B296" t="s">
         <v>2066</v>
       </c>
@@ -21268,7 +21937,10 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="297" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A297">
+        <v>65</v>
+      </c>
       <c r="B297" t="s">
         <v>2073</v>
       </c>
@@ -21303,7 +21975,10 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="298" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A298">
+        <v>65</v>
+      </c>
       <c r="B298" t="s">
         <v>2080</v>
       </c>
@@ -21338,7 +22013,10 @@
         <v>2086</v>
       </c>
     </row>
-    <row r="299" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A299">
+        <v>65</v>
+      </c>
       <c r="B299" t="s">
         <v>2087</v>
       </c>
@@ -21373,7 +22051,10 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="300" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A300">
+        <v>65</v>
+      </c>
       <c r="B300" t="s">
         <v>2094</v>
       </c>
@@ -21408,7 +22089,10 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="301" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A301">
+        <v>65</v>
+      </c>
       <c r="B301" t="s">
         <v>2101</v>
       </c>
@@ -21443,7 +22127,10 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="302" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>65</v>
+      </c>
       <c r="B302" t="s">
         <v>2108</v>
       </c>
@@ -21478,7 +22165,10 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="303" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>65</v>
+      </c>
       <c r="B303" t="s">
         <v>2115</v>
       </c>
@@ -21513,7 +22203,10 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="304" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>65</v>
+      </c>
       <c r="B304" t="s">
         <v>2122</v>
       </c>
@@ -21548,7 +22241,10 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="305" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>65</v>
+      </c>
       <c r="B305" t="s">
         <v>2129</v>
       </c>
@@ -21583,7 +22279,10 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="306" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>65</v>
+      </c>
       <c r="B306" t="s">
         <v>2136</v>
       </c>
@@ -21618,7 +22317,10 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="307" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>65</v>
+      </c>
       <c r="B307" t="s">
         <v>2143</v>
       </c>
@@ -21653,7 +22355,10 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="308" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>65</v>
+      </c>
       <c r="B308" t="s">
         <v>2150</v>
       </c>
@@ -21688,7 +22393,10 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="309" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>65</v>
+      </c>
       <c r="B309" t="s">
         <v>2157</v>
       </c>
@@ -21723,7 +22431,10 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="310" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>65</v>
+      </c>
       <c r="B310" t="s">
         <v>2164</v>
       </c>
@@ -21758,7 +22469,10 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="311" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>65</v>
+      </c>
       <c r="B311" t="s">
         <v>2171</v>
       </c>
@@ -21793,7 +22507,10 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="312" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>65</v>
+      </c>
       <c r="B312" t="s">
         <v>2178</v>
       </c>
@@ -21828,7 +22545,10 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="313" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>65</v>
+      </c>
       <c r="B313" t="s">
         <v>2184</v>
       </c>
@@ -21863,7 +22583,10 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="314" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>65</v>
+      </c>
       <c r="B314" t="s">
         <v>2191</v>
       </c>
@@ -21898,7 +22621,10 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="315" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>65</v>
+      </c>
       <c r="B315" t="s">
         <v>2198</v>
       </c>
@@ -21933,7 +22659,10 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="316" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>65</v>
+      </c>
       <c r="B316" t="s">
         <v>2205</v>
       </c>
@@ -21968,7 +22697,10 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="317" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>65</v>
+      </c>
       <c r="B317" t="s">
         <v>2212</v>
       </c>
@@ -22003,7 +22735,10 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="318" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>65</v>
+      </c>
       <c r="B318" t="s">
         <v>2219</v>
       </c>
@@ -22038,7 +22773,10 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="319" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>65</v>
+      </c>
       <c r="B319" t="s">
         <v>2226</v>
       </c>
@@ -22073,7 +22811,10 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="320" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>65</v>
+      </c>
       <c r="B320" t="s">
         <v>2233</v>
       </c>
@@ -22108,7 +22849,10 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="321" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>65</v>
+      </c>
       <c r="B321" t="s">
         <v>2240</v>
       </c>
@@ -22143,7 +22887,10 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="322" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>65</v>
+      </c>
       <c r="B322" t="s">
         <v>2247</v>
       </c>
@@ -22178,7 +22925,10 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="323" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>65</v>
+      </c>
       <c r="B323" t="s">
         <v>2254</v>
       </c>
@@ -22213,7 +22963,10 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="324" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>65</v>
+      </c>
       <c r="B324" t="s">
         <v>2261</v>
       </c>
@@ -22248,7 +23001,10 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="325" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>65</v>
+      </c>
       <c r="B325" t="s">
         <v>2268</v>
       </c>
@@ -22283,7 +23039,10 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="326" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>65</v>
+      </c>
       <c r="B326" t="s">
         <v>2275</v>
       </c>
@@ -22318,7 +23077,10 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="327" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>65</v>
+      </c>
       <c r="B327" t="s">
         <v>2282</v>
       </c>
@@ -22353,7 +23115,10 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="328" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>65</v>
+      </c>
       <c r="B328" t="s">
         <v>2289</v>
       </c>
@@ -22388,7 +23153,10 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="329" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>65</v>
+      </c>
       <c r="B329" t="s">
         <v>2296</v>
       </c>
@@ -22423,7 +23191,10 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="330" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>65</v>
+      </c>
       <c r="B330" t="s">
         <v>2303</v>
       </c>
@@ -22458,7 +23229,10 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="331" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>65</v>
+      </c>
       <c r="B331" t="s">
         <v>2310</v>
       </c>
@@ -22493,7 +23267,10 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="332" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>65</v>
+      </c>
       <c r="B332" t="s">
         <v>2317</v>
       </c>
@@ -22528,7 +23305,10 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="333" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>65</v>
+      </c>
       <c r="B333" t="s">
         <v>2324</v>
       </c>
@@ -22563,7 +23343,10 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="334" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>65</v>
+      </c>
       <c r="B334" t="s">
         <v>2331</v>
       </c>
@@ -22598,7 +23381,10 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="335" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>65</v>
+      </c>
       <c r="B335" t="s">
         <v>2338</v>
       </c>
@@ -22633,7 +23419,10 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="336" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>65</v>
+      </c>
       <c r="B336" t="s">
         <v>2345</v>
       </c>
@@ -22668,7 +23457,10 @@
         <v>2351</v>
       </c>
     </row>
-    <row r="337" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>65</v>
+      </c>
       <c r="B337" t="s">
         <v>2352</v>
       </c>
@@ -22703,7 +23495,10 @@
         <v>2358</v>
       </c>
     </row>
-    <row r="338" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>65</v>
+      </c>
       <c r="B338" t="s">
         <v>2359</v>
       </c>
@@ -22738,7 +23533,10 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="339" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>65</v>
+      </c>
       <c r="B339" t="s">
         <v>2366</v>
       </c>
@@ -22773,7 +23571,10 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="340" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>65</v>
+      </c>
       <c r="B340" t="s">
         <v>2373</v>
       </c>
@@ -22808,7 +23609,10 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="341" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>65</v>
+      </c>
       <c r="B341" t="s">
         <v>2380</v>
       </c>
@@ -22843,7 +23647,10 @@
         <v>2386</v>
       </c>
     </row>
-    <row r="342" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>65</v>
+      </c>
       <c r="B342" t="s">
         <v>2387</v>
       </c>
@@ -22878,7 +23685,10 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="343" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>65</v>
+      </c>
       <c r="B343" t="s">
         <v>2394</v>
       </c>
@@ -22913,7 +23723,10 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="344" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>65</v>
+      </c>
       <c r="B344" t="s">
         <v>2401</v>
       </c>
@@ -22948,7 +23761,10 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="345" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>65</v>
+      </c>
       <c r="B345" t="s">
         <v>2408</v>
       </c>
@@ -22983,7 +23799,10 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="346" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A346">
+        <v>65</v>
+      </c>
       <c r="B346" t="s">
         <v>2415</v>
       </c>
@@ -23018,7 +23837,10 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="347" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A347">
+        <v>65</v>
+      </c>
       <c r="B347" t="s">
         <v>2422</v>
       </c>
@@ -23053,7 +23875,10 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="348" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A348">
+        <v>65</v>
+      </c>
       <c r="B348" t="s">
         <v>2429</v>
       </c>
@@ -23088,7 +23913,10 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="349" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>65</v>
+      </c>
       <c r="B349" t="s">
         <v>2436</v>
       </c>
@@ -23123,7 +23951,10 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="350" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A350">
+        <v>65</v>
+      </c>
       <c r="B350" t="s">
         <v>2443</v>
       </c>
@@ -23158,7 +23989,10 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="351" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A351">
+        <v>65</v>
+      </c>
       <c r="B351" t="s">
         <v>2450</v>
       </c>
@@ -23193,7 +24027,10 @@
         <v>2456</v>
       </c>
     </row>
-    <row r="352" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A352">
+        <v>65</v>
+      </c>
       <c r="B352" t="s">
         <v>2457</v>
       </c>
@@ -23228,7 +24065,10 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="353" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A353">
+        <v>65</v>
+      </c>
       <c r="B353" t="s">
         <v>2464</v>
       </c>
@@ -23263,7 +24103,10 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="354" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A354">
+        <v>65</v>
+      </c>
       <c r="B354" t="s">
         <v>2471</v>
       </c>
@@ -23298,7 +24141,10 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="355" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A355">
+        <v>65</v>
+      </c>
       <c r="B355" t="s">
         <v>2478</v>
       </c>
@@ -23333,7 +24179,10 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="356" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>65</v>
+      </c>
       <c r="B356" t="s">
         <v>2485</v>
       </c>
@@ -23368,7 +24217,10 @@
         <v>2491</v>
       </c>
     </row>
-    <row r="357" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A357">
+        <v>65</v>
+      </c>
       <c r="B357" t="s">
         <v>2492</v>
       </c>
@@ -23403,7 +24255,10 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="358" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A358">
+        <v>65</v>
+      </c>
       <c r="B358" t="s">
         <v>2499</v>
       </c>
@@ -23438,7 +24293,10 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="359" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>65</v>
+      </c>
       <c r="B359" t="s">
         <v>2506</v>
       </c>
@@ -23473,7 +24331,10 @@
         <v>2512</v>
       </c>
     </row>
-    <row r="360" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A360">
+        <v>65</v>
+      </c>
       <c r="B360" t="s">
         <v>2513</v>
       </c>
@@ -23508,7 +24369,10 @@
         <v>2519</v>
       </c>
     </row>
-    <row r="361" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A361">
+        <v>65</v>
+      </c>
       <c r="B361" t="s">
         <v>2520</v>
       </c>
@@ -23543,7 +24407,10 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="362" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A362">
+        <v>65</v>
+      </c>
       <c r="B362" t="s">
         <v>2527</v>
       </c>
@@ -23578,7 +24445,10 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="363" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>65</v>
+      </c>
       <c r="B363" t="s">
         <v>2534</v>
       </c>
@@ -23613,7 +24483,10 @@
         <v>2540</v>
       </c>
     </row>
-    <row r="364" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A364">
+        <v>65</v>
+      </c>
       <c r="B364" t="s">
         <v>2541</v>
       </c>
@@ -23648,7 +24521,10 @@
         <v>2547</v>
       </c>
     </row>
-    <row r="365" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A365">
+        <v>65</v>
+      </c>
       <c r="B365" t="s">
         <v>2548</v>
       </c>
@@ -23683,7 +24559,10 @@
         <v>2554</v>
       </c>
     </row>
-    <row r="366" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A366">
+        <v>65</v>
+      </c>
       <c r="B366" t="s">
         <v>2555</v>
       </c>
@@ -23718,7 +24597,10 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="367" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A367">
+        <v>65</v>
+      </c>
       <c r="B367" t="s">
         <v>2562</v>
       </c>
@@ -23753,7 +24635,10 @@
         <v>2568</v>
       </c>
     </row>
-    <row r="368" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A368">
+        <v>65</v>
+      </c>
       <c r="B368" t="s">
         <v>2569</v>
       </c>
@@ -23788,7 +24673,10 @@
         <v>2575</v>
       </c>
     </row>
-    <row r="369" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A369">
+        <v>65</v>
+      </c>
       <c r="B369" t="s">
         <v>2576</v>
       </c>
@@ -23823,7 +24711,10 @@
         <v>2582</v>
       </c>
     </row>
-    <row r="370" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A370">
+        <v>65</v>
+      </c>
       <c r="B370" t="s">
         <v>2583</v>
       </c>
@@ -23858,7 +24749,10 @@
         <v>2589</v>
       </c>
     </row>
-    <row r="371" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A371">
+        <v>65</v>
+      </c>
       <c r="B371" t="s">
         <v>2590</v>
       </c>
@@ -23893,7 +24787,10 @@
         <v>2596</v>
       </c>
     </row>
-    <row r="372" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A372">
+        <v>65</v>
+      </c>
       <c r="B372" t="s">
         <v>2597</v>
       </c>
@@ -23928,7 +24825,10 @@
         <v>2603</v>
       </c>
     </row>
-    <row r="373" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A373">
+        <v>65</v>
+      </c>
       <c r="B373" t="s">
         <v>1230</v>
       </c>
@@ -23963,7 +24863,10 @@
         <v>2609</v>
       </c>
     </row>
-    <row r="374" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A374">
+        <v>65</v>
+      </c>
       <c r="B374" t="s">
         <v>2610</v>
       </c>
@@ -23998,7 +24901,10 @@
         <v>2616</v>
       </c>
     </row>
-    <row r="375" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A375">
+        <v>65</v>
+      </c>
       <c r="B375" t="s">
         <v>2617</v>
       </c>
@@ -24033,7 +24939,10 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="376" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A376">
+        <v>65</v>
+      </c>
       <c r="B376" t="s">
         <v>2624</v>
       </c>
@@ -24068,7 +24977,10 @@
         <v>2630</v>
       </c>
     </row>
-    <row r="377" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A377">
+        <v>65</v>
+      </c>
       <c r="B377" t="s">
         <v>2631</v>
       </c>
@@ -24103,7 +25015,10 @@
         <v>2637</v>
       </c>
     </row>
-    <row r="378" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A378">
+        <v>65</v>
+      </c>
       <c r="B378" t="s">
         <v>2638</v>
       </c>
@@ -24138,7 +25053,10 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="379" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A379">
+        <v>65</v>
+      </c>
       <c r="B379" t="s">
         <v>2645</v>
       </c>
@@ -24173,7 +25091,10 @@
         <v>2651</v>
       </c>
     </row>
-    <row r="380" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A380">
+        <v>65</v>
+      </c>
       <c r="B380" t="s">
         <v>2652</v>
       </c>
@@ -24208,7 +25129,10 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="381" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A381">
+        <v>65</v>
+      </c>
       <c r="B381" t="s">
         <v>2659</v>
       </c>
@@ -24243,7 +25167,10 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="382" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A382">
+        <v>65</v>
+      </c>
       <c r="B382" t="s">
         <v>2666</v>
       </c>
@@ -24278,7 +25205,10 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="383" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A383">
+        <v>65</v>
+      </c>
       <c r="B383" t="s">
         <v>2673</v>
       </c>
@@ -24313,7 +25243,10 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="384" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A384">
+        <v>65</v>
+      </c>
       <c r="B384" t="s">
         <v>2680</v>
       </c>
@@ -24348,7 +25281,10 @@
         <v>2686</v>
       </c>
     </row>
-    <row r="385" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A385">
+        <v>65</v>
+      </c>
       <c r="B385" t="s">
         <v>2687</v>
       </c>
@@ -24383,7 +25319,10 @@
         <v>2693</v>
       </c>
     </row>
-    <row r="386" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A386">
+        <v>65</v>
+      </c>
       <c r="B386" t="s">
         <v>2694</v>
       </c>
@@ -24418,7 +25357,10 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="387" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A387">
+        <v>65</v>
+      </c>
       <c r="B387" t="s">
         <v>2701</v>
       </c>
@@ -24453,7 +25395,10 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="388" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A388">
+        <v>65</v>
+      </c>
       <c r="B388" t="s">
         <v>2708</v>
       </c>
@@ -24488,7 +25433,10 @@
         <v>2714</v>
       </c>
     </row>
-    <row r="389" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A389">
+        <v>65</v>
+      </c>
       <c r="B389" t="s">
         <v>2715</v>
       </c>
@@ -24523,7 +25471,10 @@
         <v>2721</v>
       </c>
     </row>
-    <row r="390" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A390">
+        <v>65</v>
+      </c>
       <c r="B390" t="s">
         <v>2722</v>
       </c>
@@ -24558,7 +25509,10 @@
         <v>2728</v>
       </c>
     </row>
-    <row r="391" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A391">
+        <v>65</v>
+      </c>
       <c r="B391" t="s">
         <v>2729</v>
       </c>
@@ -24593,7 +25547,10 @@
         <v>2735</v>
       </c>
     </row>
-    <row r="392" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A392">
+        <v>65</v>
+      </c>
       <c r="B392" t="s">
         <v>2736</v>
       </c>
@@ -24628,7 +25585,10 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="393" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A393">
+        <v>65</v>
+      </c>
       <c r="B393" t="s">
         <v>2743</v>
       </c>
@@ -24663,7 +25623,10 @@
         <v>2749</v>
       </c>
     </row>
-    <row r="394" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A394">
+        <v>65</v>
+      </c>
       <c r="B394" t="s">
         <v>2750</v>
       </c>
@@ -24698,7 +25661,10 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="395" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A395">
+        <v>65</v>
+      </c>
       <c r="B395" t="s">
         <v>525</v>
       </c>
@@ -24733,7 +25699,10 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="396" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A396">
+        <v>65</v>
+      </c>
       <c r="B396" t="s">
         <v>2763</v>
       </c>
@@ -24768,7 +25737,10 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="397" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A397">
+        <v>65</v>
+      </c>
       <c r="B397" t="s">
         <v>2770</v>
       </c>
@@ -24803,7 +25775,10 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="398" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A398">
+        <v>65</v>
+      </c>
       <c r="B398" t="s">
         <v>2777</v>
       </c>
@@ -24838,7 +25813,10 @@
         <v>2783</v>
       </c>
     </row>
-    <row r="399" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A399">
+        <v>65</v>
+      </c>
       <c r="B399" t="s">
         <v>2784</v>
       </c>
@@ -24873,7 +25851,10 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="400" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A400">
+        <v>65</v>
+      </c>
       <c r="B400" t="s">
         <v>2791</v>
       </c>
@@ -24908,7 +25889,10 @@
         <v>2797</v>
       </c>
     </row>
-    <row r="401" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A401">
+        <v>65</v>
+      </c>
       <c r="B401" t="s">
         <v>2798</v>
       </c>
@@ -24943,7 +25927,10 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="402" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A402">
+        <v>65</v>
+      </c>
       <c r="B402" t="s">
         <v>2805</v>
       </c>
@@ -24978,7 +25965,10 @@
         <v>2811</v>
       </c>
     </row>
-    <row r="403" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A403">
+        <v>65</v>
+      </c>
       <c r="B403" t="s">
         <v>2812</v>
       </c>
@@ -25013,7 +26003,10 @@
         <v>2818</v>
       </c>
     </row>
-    <row r="404" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A404">
+        <v>65</v>
+      </c>
       <c r="B404" t="s">
         <v>2819</v>
       </c>
@@ -25048,7 +26041,10 @@
         <v>2825</v>
       </c>
     </row>
-    <row r="405" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A405">
+        <v>65</v>
+      </c>
       <c r="B405" t="s">
         <v>2826</v>
       </c>
@@ -25083,7 +26079,10 @@
         <v>2832</v>
       </c>
     </row>
-    <row r="406" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A406">
+        <v>65</v>
+      </c>
       <c r="B406" t="s">
         <v>2833</v>
       </c>
@@ -25118,7 +26117,10 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="407" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A407">
+        <v>65</v>
+      </c>
       <c r="B407" t="s">
         <v>2840</v>
       </c>
@@ -25153,7 +26155,10 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="408" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A408">
+        <v>65</v>
+      </c>
       <c r="B408" t="s">
         <v>2003</v>
       </c>
@@ -25188,7 +26193,10 @@
         <v>2852</v>
       </c>
     </row>
-    <row r="409" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A409">
+        <v>65</v>
+      </c>
       <c r="B409" t="s">
         <v>2853</v>
       </c>
@@ -25223,7 +26231,10 @@
         <v>2859</v>
       </c>
     </row>
-    <row r="410" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A410">
+        <v>65</v>
+      </c>
       <c r="B410" t="s">
         <v>2860</v>
       </c>
@@ -25258,7 +26269,10 @@
         <v>2866</v>
       </c>
     </row>
-    <row r="411" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A411">
+        <v>65</v>
+      </c>
       <c r="B411" t="s">
         <v>2867</v>
       </c>
@@ -25293,7 +26307,10 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="412" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A412">
+        <v>65</v>
+      </c>
       <c r="B412" t="s">
         <v>2874</v>
       </c>
@@ -25328,7 +26345,10 @@
         <v>2880</v>
       </c>
     </row>
-    <row r="413" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A413">
+        <v>65</v>
+      </c>
       <c r="B413" t="s">
         <v>2881</v>
       </c>
@@ -25363,7 +26383,10 @@
         <v>2887</v>
       </c>
     </row>
-    <row r="414" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A414">
+        <v>65</v>
+      </c>
       <c r="B414" t="s">
         <v>2888</v>
       </c>
@@ -25398,7 +26421,10 @@
         <v>2894</v>
       </c>
     </row>
-    <row r="415" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A415">
+        <v>65</v>
+      </c>
       <c r="B415" t="s">
         <v>2895</v>
       </c>
@@ -25433,7 +26459,10 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="416" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A416">
+        <v>65</v>
+      </c>
       <c r="B416" t="s">
         <v>2902</v>
       </c>
@@ -25468,7 +26497,10 @@
         <v>2908</v>
       </c>
     </row>
-    <row r="417" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A417">
+        <v>65</v>
+      </c>
       <c r="B417" t="s">
         <v>2909</v>
       </c>
@@ -25503,7 +26535,10 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="418" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A418">
+        <v>65</v>
+      </c>
       <c r="B418" t="s">
         <v>2916</v>
       </c>
@@ -25538,7 +26573,10 @@
         <v>2922</v>
       </c>
     </row>
-    <row r="419" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A419">
+        <v>65</v>
+      </c>
       <c r="B419" t="s">
         <v>385</v>
       </c>
@@ -25573,7 +26611,10 @@
         <v>2928</v>
       </c>
     </row>
-    <row r="420" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A420">
+        <v>65</v>
+      </c>
       <c r="B420" t="s">
         <v>2929</v>
       </c>
@@ -25608,7 +26649,10 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="421" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A421">
+        <v>65</v>
+      </c>
       <c r="B421" t="s">
         <v>2936</v>
       </c>
@@ -25643,7 +26687,10 @@
         <v>2942</v>
       </c>
     </row>
-    <row r="422" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A422">
+        <v>65</v>
+      </c>
       <c r="B422" t="s">
         <v>2943</v>
       </c>
@@ -25678,7 +26725,10 @@
         <v>2949</v>
       </c>
     </row>
-    <row r="423" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A423">
+        <v>65</v>
+      </c>
       <c r="B423" t="s">
         <v>2950</v>
       </c>
@@ -25713,7 +26763,10 @@
         <v>2956</v>
       </c>
     </row>
-    <row r="424" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A424">
+        <v>65</v>
+      </c>
       <c r="B424" t="s">
         <v>2957</v>
       </c>
@@ -25748,7 +26801,10 @@
         <v>2963</v>
       </c>
     </row>
-    <row r="425" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A425">
+        <v>65</v>
+      </c>
       <c r="B425" t="s">
         <v>2964</v>
       </c>
@@ -25783,7 +26839,10 @@
         <v>2970</v>
       </c>
     </row>
-    <row r="426" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A426">
+        <v>65</v>
+      </c>
       <c r="B426" t="s">
         <v>2971</v>
       </c>
@@ -25818,7 +26877,10 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="427" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A427">
+        <v>65</v>
+      </c>
       <c r="B427" t="s">
         <v>2978</v>
       </c>
@@ -25853,7 +26915,10 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="428" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A428">
+        <v>65</v>
+      </c>
       <c r="B428" t="s">
         <v>2985</v>
       </c>
@@ -25888,7 +26953,10 @@
         <v>2991</v>
       </c>
     </row>
-    <row r="429" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A429">
+        <v>65</v>
+      </c>
       <c r="B429" t="s">
         <v>2992</v>
       </c>
@@ -25923,7 +26991,10 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="430" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A430">
+        <v>65</v>
+      </c>
       <c r="B430" t="s">
         <v>2999</v>
       </c>
@@ -25958,7 +27029,10 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="431" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A431">
+        <v>65</v>
+      </c>
       <c r="B431" t="s">
         <v>3006</v>
       </c>
@@ -25993,7 +27067,10 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="432" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A432">
+        <v>65</v>
+      </c>
       <c r="B432" t="s">
         <v>3013</v>
       </c>
@@ -26028,7 +27105,10 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="433" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A433">
+        <v>65</v>
+      </c>
       <c r="B433" t="s">
         <v>3020</v>
       </c>
@@ -26063,7 +27143,10 @@
         <v>3026</v>
       </c>
     </row>
-    <row r="434" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A434">
+        <v>65</v>
+      </c>
       <c r="B434" t="s">
         <v>3027</v>
       </c>
@@ -26098,7 +27181,10 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="435" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A435">
+        <v>65</v>
+      </c>
       <c r="B435" t="s">
         <v>3034</v>
       </c>
@@ -26133,7 +27219,10 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="436" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A436">
+        <v>65</v>
+      </c>
       <c r="B436" t="s">
         <v>3041</v>
       </c>
@@ -26168,7 +27257,10 @@
         <v>3047</v>
       </c>
     </row>
-    <row r="437" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A437">
+        <v>65</v>
+      </c>
       <c r="B437" t="s">
         <v>3048</v>
       </c>
@@ -26203,7 +27295,10 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="438" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A438">
+        <v>65</v>
+      </c>
       <c r="B438" t="s">
         <v>3055</v>
       </c>
@@ -26238,7 +27333,10 @@
         <v>3061</v>
       </c>
     </row>
-    <row r="439" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A439">
+        <v>65</v>
+      </c>
       <c r="B439" t="s">
         <v>2212</v>
       </c>
@@ -26273,7 +27371,10 @@
         <v>3067</v>
       </c>
     </row>
-    <row r="440" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A440">
+        <v>65</v>
+      </c>
       <c r="B440" t="s">
         <v>126</v>
       </c>
@@ -26308,7 +27409,10 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="441" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A441">
+        <v>65</v>
+      </c>
       <c r="B441" t="s">
         <v>336</v>
       </c>
@@ -26343,7 +27447,10 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="442" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A442">
+        <v>65</v>
+      </c>
       <c r="B442" t="s">
         <v>3080</v>
       </c>
@@ -26378,7 +27485,10 @@
         <v>3086</v>
       </c>
     </row>
-    <row r="443" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A443">
+        <v>65</v>
+      </c>
       <c r="B443" t="s">
         <v>3087</v>
       </c>
@@ -26413,7 +27523,10 @@
         <v>3093</v>
       </c>
     </row>
-    <row r="444" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A444">
+        <v>65</v>
+      </c>
       <c r="B444" t="s">
         <v>3094</v>
       </c>
@@ -26448,7 +27561,10 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="445" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A445">
+        <v>65</v>
+      </c>
       <c r="B445" t="s">
         <v>3101</v>
       </c>
@@ -26483,7 +27599,10 @@
         <v>3107</v>
       </c>
     </row>
-    <row r="446" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A446">
+        <v>65</v>
+      </c>
       <c r="B446" t="s">
         <v>3020</v>
       </c>
@@ -26518,7 +27637,10 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="447" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A447">
+        <v>65</v>
+      </c>
       <c r="B447" t="s">
         <v>3114</v>
       </c>
@@ -26553,7 +27675,10 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="448" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A448">
+        <v>65</v>
+      </c>
       <c r="B448" t="s">
         <v>3121</v>
       </c>
@@ -26588,7 +27713,10 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="449" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A449">
+        <v>65</v>
+      </c>
       <c r="B449" t="s">
         <v>3128</v>
       </c>
@@ -26623,7 +27751,10 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="450" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A450">
+        <v>65</v>
+      </c>
       <c r="B450" t="s">
         <v>3135</v>
       </c>
@@ -26658,7 +27789,10 @@
         <v>3141</v>
       </c>
     </row>
-    <row r="451" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A451">
+        <v>65</v>
+      </c>
       <c r="B451" t="s">
         <v>3142</v>
       </c>
@@ -26693,7 +27827,10 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="452" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A452">
+        <v>65</v>
+      </c>
       <c r="B452" t="s">
         <v>3149</v>
       </c>
@@ -26728,7 +27865,10 @@
         <v>3155</v>
       </c>
     </row>
-    <row r="453" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A453">
+        <v>65</v>
+      </c>
       <c r="B453" t="s">
         <v>1635</v>
       </c>
@@ -26763,7 +27903,10 @@
         <v>3161</v>
       </c>
     </row>
-    <row r="454" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A454">
+        <v>65</v>
+      </c>
       <c r="B454" t="s">
         <v>3162</v>
       </c>
@@ -26798,7 +27941,10 @@
         <v>3168</v>
       </c>
     </row>
-    <row r="455" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A455">
+        <v>65</v>
+      </c>
       <c r="B455" t="s">
         <v>3169</v>
       </c>
@@ -26833,7 +27979,10 @@
         <v>3175</v>
       </c>
     </row>
-    <row r="456" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A456">
+        <v>65</v>
+      </c>
       <c r="B456" t="s">
         <v>3176</v>
       </c>
@@ -26868,7 +28017,10 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="457" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A457">
+        <v>65</v>
+      </c>
       <c r="B457" t="s">
         <v>3183</v>
       </c>
@@ -26903,7 +28055,10 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="458" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A458">
+        <v>65</v>
+      </c>
       <c r="B458" t="s">
         <v>3190</v>
       </c>
@@ -26938,7 +28093,10 @@
         <v>3196</v>
       </c>
     </row>
-    <row r="459" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A459">
+        <v>65</v>
+      </c>
       <c r="B459" t="s">
         <v>3197</v>
       </c>
@@ -26973,7 +28131,10 @@
         <v>3202</v>
       </c>
     </row>
-    <row r="460" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A460">
+        <v>65</v>
+      </c>
       <c r="B460" t="s">
         <v>3203</v>
       </c>
@@ -27008,7 +28169,10 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="461" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A461">
+        <v>65</v>
+      </c>
       <c r="B461" t="s">
         <v>3210</v>
       </c>
@@ -27043,7 +28207,10 @@
         <v>3216</v>
       </c>
     </row>
-    <row r="462" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A462">
+        <v>65</v>
+      </c>
       <c r="B462" t="s">
         <v>3217</v>
       </c>
@@ -27078,7 +28245,10 @@
         <v>3223</v>
       </c>
     </row>
-    <row r="463" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A463">
+        <v>65</v>
+      </c>
       <c r="B463" t="s">
         <v>3224</v>
       </c>
@@ -27113,7 +28283,10 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="464" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A464">
+        <v>65</v>
+      </c>
       <c r="B464" t="s">
         <v>98</v>
       </c>
@@ -27148,7 +28321,10 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="465" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A465">
+        <v>65</v>
+      </c>
       <c r="B465" t="s">
         <v>3237</v>
       </c>
@@ -27183,7 +28359,10 @@
         <v>3243</v>
       </c>
     </row>
-    <row r="466" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A466">
+        <v>65</v>
+      </c>
       <c r="B466" t="s">
         <v>3244</v>
       </c>
@@ -27218,7 +28397,10 @@
         <v>3250</v>
       </c>
     </row>
-    <row r="467" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A467">
+        <v>65</v>
+      </c>
       <c r="B467" t="s">
         <v>3251</v>
       </c>
@@ -27253,7 +28435,10 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="468" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A468">
+        <v>65</v>
+      </c>
       <c r="B468" t="s">
         <v>3258</v>
       </c>
@@ -27288,7 +28473,10 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="469" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A469">
+        <v>65</v>
+      </c>
       <c r="B469" t="s">
         <v>3265</v>
       </c>
@@ -27323,7 +28511,10 @@
         <v>3271</v>
       </c>
     </row>
-    <row r="470" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A470">
+        <v>65</v>
+      </c>
       <c r="B470" t="s">
         <v>3272</v>
       </c>
@@ -27358,7 +28549,10 @@
         <v>3278</v>
       </c>
     </row>
-    <row r="471" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A471">
+        <v>65</v>
+      </c>
       <c r="B471" t="s">
         <v>3279</v>
       </c>
@@ -27393,7 +28587,10 @@
         <v>3285</v>
       </c>
     </row>
-    <row r="472" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A472">
+        <v>65</v>
+      </c>
       <c r="B472" t="s">
         <v>3286</v>
       </c>
@@ -27428,7 +28625,10 @@
         <v>3292</v>
       </c>
     </row>
-    <row r="473" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A473">
+        <v>65</v>
+      </c>
       <c r="B473" t="s">
         <v>3293</v>
       </c>
@@ -27463,7 +28663,10 @@
         <v>3299</v>
       </c>
     </row>
-    <row r="474" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A474">
+        <v>65</v>
+      </c>
       <c r="B474" t="s">
         <v>3300</v>
       </c>
@@ -27498,7 +28701,10 @@
         <v>3306</v>
       </c>
     </row>
-    <row r="475" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A475">
+        <v>65</v>
+      </c>
       <c r="B475" t="s">
         <v>3307</v>
       </c>
@@ -27533,7 +28739,10 @@
         <v>3313</v>
       </c>
     </row>
-    <row r="476" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A476">
+        <v>65</v>
+      </c>
       <c r="B476" t="s">
         <v>3314</v>
       </c>
@@ -27568,7 +28777,10 @@
         <v>3320</v>
       </c>
     </row>
-    <row r="477" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A477">
+        <v>65</v>
+      </c>
       <c r="B477" t="s">
         <v>3321</v>
       </c>
@@ -27603,7 +28815,10 @@
         <v>3327</v>
       </c>
     </row>
-    <row r="478" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A478">
+        <v>65</v>
+      </c>
       <c r="B478" t="s">
         <v>3328</v>
       </c>
@@ -27638,7 +28853,10 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="479" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A479">
+        <v>65</v>
+      </c>
       <c r="B479" t="s">
         <v>3335</v>
       </c>
@@ -27673,7 +28891,10 @@
         <v>3341</v>
       </c>
     </row>
-    <row r="480" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A480">
+        <v>65</v>
+      </c>
       <c r="B480" t="s">
         <v>3342</v>
       </c>
@@ -27708,7 +28929,10 @@
         <v>3348</v>
       </c>
     </row>
-    <row r="481" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A481">
+        <v>65</v>
+      </c>
       <c r="B481" t="s">
         <v>3349</v>
       </c>
@@ -27743,7 +28967,10 @@
         <v>3355</v>
       </c>
     </row>
-    <row r="482" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A482">
+        <v>65</v>
+      </c>
       <c r="B482" t="s">
         <v>3356</v>
       </c>
@@ -27778,7 +29005,10 @@
         <v>3362</v>
       </c>
     </row>
-    <row r="483" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A483">
+        <v>65</v>
+      </c>
       <c r="B483" t="s">
         <v>3363</v>
       </c>
@@ -27813,7 +29043,10 @@
         <v>3369</v>
       </c>
     </row>
-    <row r="484" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A484">
+        <v>65</v>
+      </c>
       <c r="B484" t="s">
         <v>3370</v>
       </c>
@@ -27848,7 +29081,10 @@
         <v>3376</v>
       </c>
     </row>
-    <row r="485" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A485">
+        <v>65</v>
+      </c>
       <c r="B485" t="s">
         <v>3377</v>
       </c>
@@ -27883,7 +29119,10 @@
         <v>3383</v>
       </c>
     </row>
-    <row r="486" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A486">
+        <v>65</v>
+      </c>
       <c r="B486" t="s">
         <v>3384</v>
       </c>
@@ -27918,7 +29157,10 @@
         <v>3390</v>
       </c>
     </row>
-    <row r="487" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A487">
+        <v>65</v>
+      </c>
       <c r="B487" t="s">
         <v>3391</v>
       </c>
@@ -27953,7 +29195,10 @@
         <v>3397</v>
       </c>
     </row>
-    <row r="488" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A488">
+        <v>65</v>
+      </c>
       <c r="B488" t="s">
         <v>3398</v>
       </c>
@@ -27988,7 +29233,10 @@
         <v>3404</v>
       </c>
     </row>
-    <row r="489" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A489">
+        <v>65</v>
+      </c>
       <c r="B489" t="s">
         <v>3405</v>
       </c>
@@ -28023,7 +29271,10 @@
         <v>3411</v>
       </c>
     </row>
-    <row r="490" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A490">
+        <v>65</v>
+      </c>
       <c r="B490" t="s">
         <v>3412</v>
       </c>
@@ -28058,7 +29309,10 @@
         <v>3418</v>
       </c>
     </row>
-    <row r="491" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A491">
+        <v>65</v>
+      </c>
       <c r="B491" t="s">
         <v>3419</v>
       </c>
@@ -28093,7 +29347,7 @@
         <v>3425</v>
       </c>
     </row>
-    <row r="492" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B492" t="s">
         <v>3426</v>
       </c>
@@ -28128,7 +29382,7 @@
         <v>3432</v>
       </c>
     </row>
-    <row r="493" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B493" t="s">
         <v>3433</v>
       </c>
@@ -28163,7 +29417,7 @@
         <v>3439</v>
       </c>
     </row>
-    <row r="494" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B494" t="s">
         <v>3440</v>
       </c>
@@ -28198,7 +29452,7 @@
         <v>3446</v>
       </c>
     </row>
-    <row r="495" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B495" t="s">
         <v>3447</v>
       </c>
@@ -28233,7 +29487,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="496" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B496" t="s">
         <v>1705</v>
       </c>
